--- a/extenbooks/ES1704.xlsx
+++ b/extenbooks/ES1704.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 8</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1972–1995</t>
+          <t>1972-1995</t>
         </is>
       </c>
     </row>
@@ -834,174 +834,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1704-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cronin 2001 RPE Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1704 — NZ Total Value (Cronin 2001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study (Cronin 2001 RPE Table 1)</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t># ES1704 — NZ Total Value (Cronin 2001)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Period**: [1972, 1995]</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Units**: share</t>
+          <t>**Chapter**: External study (Cronin 2001 RPE Table 1)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Period**: [1972, 1995]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Units**: share</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Cronin Table 1, NZ total value in millions of NZD.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cronin Table 1, NZ total value in millions of NZD.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>`data/source/external_studies/Cronin2001_cronin_table1_nzsna_classical_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1704_nz_total_value_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1704_nz_total_value_cronin2001.py`.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Validation</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Cronin2001_cronin_table1_nzsna_classical_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1704_nz_total_value_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1704_nz_total_value_cronin2001.py`.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Validation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Provenance</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/source/external_studies/Cronin2001_cronin_table1_nzsna_classical_1972_1995.csv</t>
+          <t>## Provenance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; L01_ES1704 -&gt; data/intermediate/ES1704.csv</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; P02_ES1704 -&gt; data/final/ES1704.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1010,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; V03_ES1704 -&gt; data/intermediate/validation/ES1704.json</t>
+          <t>data/source/external_studies/Cronin2001_cronin_table1_nzsna_classical_1972_1995.csv</t>
         </is>
       </c>
     </row>
@@ -1017,53 +1018,77 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  -&gt; L01_ES1704 -&gt; data/intermediate/ES1704.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; P02_ES1704 -&gt; data/final/ES1704.csv</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t xml:space="preserve">  -&gt; V03_ES1704 -&gt; data/intermediate/validation/ES1704.json</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A Mapping of the New Zealand System of National Accounts to Classical Economic Categories, 1972-1995.' Review of Political Economy 13(3): 309-327.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A Mapping of the New Zealand System of National Accounts to Classical Economic Categories, 1972-1995.' Review of Political Economy 13(3): 309-327.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -1080,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1108,197 +1133,241 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Total value (TV) is the classical economic concept of value produced in the productive and trading sectors: TV = c + v + s (constant capital plus variable capital plus surplus-value). It excludes unproductive activities such as finance, government administration, police, courts, defence, and royalty flows (ground rent, interest, patents, taxes). TV is derived by mapping NZSNA data to classical categories for 25 NZ production groups, following Shaikh-Tonak (1994). TV is systematically lower than neoclassical gross output because unproductive sectors are excluded, and lower than GDP for different reasons (GDP = v + s, while TV includes intermediate consumption of productive industries).</t>
+          <t>However, much of the activity classified as productive in neoclassical analysis must be isolated to derive the classical economic categories of value, production and trade. Production of goods or services realises value only when it is sold. Trade, while unproductive, is a necessary part of the realisation of value. The total value produced within an economy then in classical terms represents the sale of produced goods and services, summarised in Fig. 2 (Shaikh &amp; Tonak, 1994, p. 72).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 3 (Mapping Total Value); SUMMARY.md</t>
+          <t>Cronin_2001, body_text.md Section 3 (Mapping Total Value)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Series ES1704-A: Digitized from Cronin (2001) Table 1, column 'Total value', 1972-1995 (24 observations). Original table title: 'NZSNA in classical categories ($m)', Review of Political Economy 13(3), p. 11 (Table 1). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Units: millions NZD, current prices.</t>
+          <t>The differing conventional and classical views arise from the differing conceptions of productive activity. The conventional category of gross output increases faster than the classical concept of total value, particularly during the late 1980s and early 1990s, because of the growth of classically unproductive activity in the economy in this period (Fig. 13). The growth of unproductive activity can be seen in the relationship of total wages to variable capital, the latter growing more quickly, reflecting the growth of unproductive employment.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 1; tables.csv rows 2-26</t>
+          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Annual total value (millions NZD, current prices): 1972=10423, 1973=12267, 1974=14233, 1975=15553, 1976=18847, 1977=23454, 1978=25195, 1979=28131, 1980=33317, 1981=38400, 1982=46691, 1983=52322, 1984=57628, 1985=67193, 1986=77232, 1987=87537, 1988=93389, 1989=96845, 1990=100038, 1991=100112, 1992=100125, 1993=105252, 1994=115853, 1995=123284.</t>
+          <t>In summary, the classical economic category of total value can be derived from the NZSNA data by separating the elements of production and trade from those of money flows and non-capitalist activity. This is a simple mapping process, with the exception of the NZSNA categories trade, finance, and owner-occupied dwellings, which are adjusted along the lines described by Shaikh &amp; Tonak (1994, pp. 253-254, 269-270).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 1; tables.csv</t>
+          <t>Cronin_2001, body_text.md Section 3 (Deriving Components of Value)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TV rose from NZD 10,423m in 1972 to NZD 123,284m in 1995, an increase of 1,083% in nominal terms. Gross output rose faster (1,196% over the same period, from 12,469m to 161,646m), reflecting the expansion of unproductive activity. The gap between gross output and total value widened notably from the late 1980s, as the financial sector and other unproductive industries grew rapidly following Rogernomics deregulation. The near-stagnation of TV in 1990-1992 (100,038 to 100,125) reflects real productive sector weakness during the post-reform recession, while gross output continued rising.</t>
+          <t>Non-capitalist production in New Zealand is insignificant, however, with the most likely candidate — farming — being undertaken predominately by owner-producers with relatively large and highly mechanised holdings. There is insufficient data in the national accounts and from other sources to identify the small amount of non-capitalist output produced by the self-employed and non-profit institutions, however. So, for the purposes of this study, all marketed production is assumed to be capitalist.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+          <t>Cronin_2001, body_text.md Section 3 (Non-Capitalist Production)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>components</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TV components for terminal years from Table 1: 1972 — c=5,094m, v=1,739m, s=3,589m, TV=10,423m. 1995 — c=60,887m, v=15,347m, s=47,049m, TV=123,284m. Growth rates 1972-1995: c +1,095%, v +783%, s +1,211%, TV +1,083%. Surplus-value grew fastest, reflecting the rising rate of exploitation. Variable capital grew slowest, consistent with the rising rate of surplus-value (s/v from 206% to 307%).</t>
+          <t>Total value (TV) is the classical economic concept of value produced in the productive and trading sectors: TV = c + v + s (constant capital plus variable capital plus surplus-value). It excludes unproductive activities such as finance, government administration, police, courts, defence, and royalty flows (ground rent, interest, patents, taxes). TV is derived by mapping NZSNA data to classical categories for 25 NZ production groups, following Shaikh-Tonak (1994). TV is systematically lower than neoclassical gross output because unproductive sectors are excluded, and lower than GDP for different reasons (GDP = v + s, while TV includes intermediate consumption of productive industries).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 1; SUMMARY.md</t>
+          <t>Cronin_2001, body_text.md Section 3 (Mapping Total Value); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unproductive_activity</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The divergence between gross output (neoclassical) and total value (classical) is the key empirical indicator of unproductive activity growth. In 1972 TV was 83.6% of gross output (10,423 / 12,469). By 1995 TV was 76.3% of gross output (123,284 / 161,646). This widening gap quantifies the increasing share of the economy devoted to classically unproductive activities — financial services, wholesale/retail trade beyond production-serving functions, government administration — that appear in GDP and gross output but not in classical total value.</t>
+          <t>Series ES1704-A: Digitized from Cronin (2001) Table 1, column 'Total value', 1972-1995 (24 observations). Original table title: 'NZSNA in classical categories ($m)', Review of Political Economy 13(3), p. 11 (Table 1). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Units: millions NZD, current prices.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+          <t>Cronin_2001, Table 1; tables.csv rows 2-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cronin Fig 13: plots gross output vs total value 1972-1995, showing the divergence particularly from the late 1980s as unproductive activity expanded. Fig 14: compares GDP growth with classical value-added (v + s) growth, showing these do not consistently diverge — the divergence is at the gross output/total value level, not the net value-added level.</t>
+          <t>Annual total value (millions NZD, current prices): 1972=10423, 1973=12267, 1974=14233, 1975=15553, 1976=18847, 1977=23454, 1978=25195, 1979=28131, 1980=33317, 1981=38400, 1982=46691, 1983=52322, 1984=57628, 1985=67193, 1986=77232, 1987=87537, 1988=93389, 1989=96845, 1990=100038, 1991=100112, 1992=100125, 1993=105252, 1994=115853, 1995=123284.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5</t>
+          <t>Cronin_2001, Table 1; tables.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>price_note</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>All TV values are in current prices (nominal NZD millions). No deflator is applied in Cronin's presentation; the classical framework treats value flows at current prices. Comparisons across time should account for NZ inflation, which was substantial over the 1972-1995 period (particularly the high-inflation 1970s-1980s).</t>
+          <t>TV rose from NZD 10,423m in 1972 to NZD 123,284m in 1995, an increase of 1,083% in nominal terms. Gross output rose faster (1,196% over the same period, from 12,469m to 161,646m), reflecting the expansion of unproductive activity. The gap between gross output and total value widened notably from the late 1980s, as the financial sector and other unproductive industries grew rapidly following Rogernomics deregulation. The near-stagnation of TV in 1990-1992 (100,038 to 100,125) reflects real productive sector weakness during the post-reform recession, while gross output continued rising.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 1 header</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>components</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TV components for terminal years from Table 1: 1972 — c=5,094m, v=1,739m, s=3,589m, TV=10,423m. 1995 — c=60,887m, v=15,347m, s=47,049m, TV=123,284m. Growth rates 1972-1995: c +1,095%, v +783%, s +1,211%, TV +1,083%. Surplus-value grew fastest, reflecting the rising rate of exploitation. Variable capital grew slowest, consistent with the rising rate of surplus-value (s/v from 206% to 307%).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cronin_2001, Table 1; SUMMARY.md</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>unproductive_activity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Total value in millions NZD directly digitized from Cronin (2001) Table 1. Classical concept excluding unproductive sectors; derived from NZSNA mapped to classical categories for 25 NZ production groups, 1972-1995. Current prices. No extension beyond 1995.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>The divergence between gross output (neoclassical) and total value (classical) is the key empirical indicator of unproductive activity growth. In 1972 TV was 83.6% of gross output (10,423 / 12,469). By 1995 TV was 76.3% of gross output (123,284 / 161,646). This widening gap quantifies the increasing share of the economy devoted to classically unproductive activities — financial services, wholesale/retail trade beyond production-serving functions, government administration — that appear in GDP and gross output but not in classical total value.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cronin Fig 13: plots gross output vs total value 1972-1995, showing the divergence particularly from the late 1980s as unproductive activity expanded. Fig 14: compares GDP growth with classical value-added (v + s) growth, showing these do not consistently diverge — the divergence is at the gross output/total value level, not the net value-added level.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 5</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>price_note</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>All TV values are in current prices (nominal NZD millions). No deflator is applied in Cronin's presentation; the classical framework treats value flows at current prices. Comparisons across time should account for NZ inflation, which was substantial over the 1972-1995 period (particularly the high-inflation 1970s-1980s).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cronin_2001, Table 1 header</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Total value in millions NZD directly digitized from Cronin (2001) Table 1. Classical concept excluding unproductive sectors; derived from NZSNA mapped to classical categories for 25 NZ production groups, 1972-1995. Current prices. No extension beyond 1995.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>known_issues:</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
         <is>
           <t>No post-1995 extension available from this source</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Nominal (current price) series only; no real deflated version available from Cronin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NZSNA adjustments required for trade, finance, and owner-occupied dwellings (following ST 1994, pp. 253-254, 269-270) introduce some estimation uncertainty</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Non-capitalist production assumed negligible — Cronin notes this introduces a small upward bias in TV</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1375,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ES1701</t>
+          <t>NZSNA adjustments required for trade, finance, and owner-occupied dwellings (following ST 1994, pp. 253-254, 269-270) introduce some estimation uncertainty</t>
         </is>
       </c>
     </row>
@@ -1314,45 +1383,69 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Non-capitalist production assumed negligible — Cronin notes this introduces a small upward bias in TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ES1701</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>ES1702</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>ES1703</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Cronin_2001</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1369,7 +1462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1432,7 +1525,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1478,6 +1571,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
